--- a/data/valuations/DE/DE_modelo_valoracion.xlsx
+++ b/data/valuations/DE/DE_modelo_valoracion.xlsx
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.169</v>
+        <v>0.1495</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.1521</v>
+        <v>0.13455</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.1352</v>
+        <v>0.1196</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.1183</v>
+        <v>0.10465</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.1014</v>
+        <v>0.08969999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.091</v>
+        <v>0.1105</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.0819</v>
+        <v>0.09945</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.0728</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.06369999999999999</v>
+        <v>0.07735</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.0546</v>
+        <v>0.0663</v>
       </c>
     </row>
     <row r="11">
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.3769251909068355</v>
+        <v>0.3669251909068355</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.3769251909068355</v>
+        <v>0.3669251909068355</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.3769251909068355</v>
+        <v>0.3669251909068355</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.3769251909068355</v>
+        <v>0.3669251909068355</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.3769251909068355</v>
+        <v>0.3669251909068355</v>
       </c>
     </row>
     <row r="17">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.3369251909068355</v>
+        <v>0.3469251909068355</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.3369251909068355</v>
+        <v>0.3469251909068355</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.3369251909068355</v>
+        <v>0.3469251909068355</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.3369251909068355</v>
+        <v>0.3469251909068355</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.3369251909068355</v>
+        <v>0.3469251909068355</v>
       </c>
     </row>
     <row r="18">
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.07169141166514646</v>
+        <v>0.07669141166514645</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.07169141166514646</v>
+        <v>0.07669141166514645</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.07169141166514646</v>
+        <v>0.07669141166514645</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.07169141166514646</v>
+        <v>0.07669141166514645</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.07169141166514646</v>
+        <v>0.07669141166514645</v>
       </c>
     </row>
     <row r="22">
@@ -912,19 +912,19 @@
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.09169141166514645</v>
+        <v>0.08669141166514646</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.09169141166514645</v>
+        <v>0.08669141166514646</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.09169141166514645</v>
+        <v>0.08669141166514646</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.09169141166514645</v>
+        <v>0.08669141166514646</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.09169141166514645</v>
+        <v>0.08669141166514646</v>
       </c>
     </row>
     <row r="23">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.04762228268028432</v>
+        <v>0.04262228268028432</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.04762228268028432</v>
+        <v>0.04262228268028432</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.04762228268028432</v>
+        <v>0.04262228268028432</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.04762228268028432</v>
+        <v>0.04262228268028432</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.04762228268028432</v>
+        <v>0.04262228268028432</v>
       </c>
     </row>
     <row r="28">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.08443542207956548</v>
+        <v>0.08441019330630305</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.08443542207956548</v>
+        <v>0.08441019330630305</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.08443542207956548</v>
+        <v>0.08441019330630305</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.08443542207956548</v>
+        <v>0.08441019330630305</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.08443542207956548</v>
+        <v>0.08441019330630305</v>
       </c>
     </row>
     <row r="32">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.0813</v>
+        <v>0.0843</v>
       </c>
     </row>
     <row r="36">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.0713</v>
+        <v>0.0743</v>
       </c>
     </row>
     <row r="37">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.1013</v>
+        <v>0.09429999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43">
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>589.77</v>
+        <v>566.64</v>
       </c>
     </row>
     <row r="4">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="K21" s="8">
-        <f>K12*$C$16</f>
+        <f>K8*$C$16</f>
         <v/>
       </c>
     </row>
@@ -3652,11 +3652,11 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>(-) Net Debt ($M)</t>
+          <t>(-) Net Debt ($M) [ajustada — excl. Financial Services]</t>
         </is>
       </c>
       <c r="C29" s="18" t="n">
-        <v>-55974</v>
+        <v>-657</v>
       </c>
     </row>
     <row r="30">
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/589.77-1</f>
+        <f>C33/566.64-1</f>
         <v/>
       </c>
     </row>
@@ -3753,176 +3753,176 @@
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.0513</v>
+        <v>0.0543</v>
       </c>
       <c r="C39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*8/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*8/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*10/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*10/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*12/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*12/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*14/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*14/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*16/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*16/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.06129999999999999</v>
+        <v>0.0643</v>
       </c>
       <c r="C40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*8/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*8/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*10/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*10/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*12/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*12/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*14/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*14/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*16/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*16/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.0713</v>
+        <v>0.0743</v>
       </c>
       <c r="C41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*8/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*8/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*10/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*10/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*12/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*12/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*14/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*14/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*16/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*16/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.0813</v>
+        <v>0.0843</v>
       </c>
       <c r="C42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*8/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*8/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*10/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*10/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*12/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*12/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*14/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*14/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*16/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*16/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.09129999999999999</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="C43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*8/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*8/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*10/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*10/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*12/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*12/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*14/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*14/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*16/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*16/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.1013</v>
+        <v>0.1043</v>
       </c>
       <c r="C44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*8/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*8/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*10/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*10/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*12/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*12/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*14/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*14/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*16/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*16/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.1113</v>
+        <v>0.1143</v>
       </c>
       <c r="C45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*8/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*8/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*10/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*10/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*12/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*12/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*14/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*14/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*16/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*16/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>

--- a/data/valuations/DE/DE_modelo_valoracion.xlsx
+++ b/data/valuations/DE/DE_modelo_valoracion.xlsx
@@ -638,19 +638,19 @@
         </is>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.13</v>
+        <v>-0.091</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.117</v>
+        <v>-0.07100000000000001</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.104</v>
+        <v>-0.051</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.091</v>
+        <v>-0.031</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.078</v>
+        <v>-0.011</v>
       </c>
     </row>
     <row r="9">
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.1495</v>
+        <v>-0.07435</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.13455</v>
+        <v>-0.05435</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.1196</v>
+        <v>-0.03435000000000001</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.10465</v>
+        <v>-0.01435</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.08969999999999999</v>
+        <v>0.005650000000000002</v>
       </c>
     </row>
     <row r="10">
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.1105</v>
+        <v>-0.10765</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.09945</v>
+        <v>-0.08764999999999998</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.08840000000000001</v>
+        <v>-0.06764999999999999</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.07735</v>
+        <v>-0.04764999999999998</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.0663</v>
+        <v>-0.02764999999999998</v>
       </c>
     </row>
     <row r="11">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.0843</v>
+        <v>0.0872</v>
       </c>
     </row>
     <row r="36">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.0743</v>
+        <v>0.0772</v>
       </c>
     </row>
     <row r="37">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.09719999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41">
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="C41" s="9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43">
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>566.64</v>
+        <v>575.71</v>
       </c>
     </row>
     <row r="4">
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/566.64-1</f>
+        <f>C33/575.71-1</f>
         <v/>
       </c>
     </row>
@@ -3727,202 +3727,202 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>8x</t>
+          <t>7x</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>10x</t>
+          <t>9x</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>12x</t>
+          <t>11x</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>14x</t>
+          <t>13x</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>16x</t>
+          <t>15x</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.0543</v>
+        <v>0.0572</v>
       </c>
       <c r="C39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*8/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*7/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*10/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*9/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*12/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*11/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*14/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*13/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*16/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*15/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.0643</v>
+        <v>0.0672</v>
       </c>
       <c r="C40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*8/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*7/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*10/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*9/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*12/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*11/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*14/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*13/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*16/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*15/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.0743</v>
+        <v>0.0772</v>
       </c>
       <c r="C41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*8/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*7/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*10/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*9/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*12/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*11/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*14/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*13/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*16/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*15/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.0843</v>
+        <v>0.0872</v>
       </c>
       <c r="C42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*8/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*7/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*10/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*9/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*12/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*11/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*14/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*13/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*16/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*15/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="C43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*8/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*7/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*10/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*9/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*12/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*11/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*14/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*13/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*16/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*15/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.1043</v>
+        <v>0.1072</v>
       </c>
       <c r="C44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*8/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*7/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*10/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*9/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*12/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*11/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*14/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*13/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*16/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*15/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.1143</v>
+        <v>0.1172</v>
       </c>
       <c r="C45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*8/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*7/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*10/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*9/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*12/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*11/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*14/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*13/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*16/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*15/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>

--- a/data/valuations/DE/DE_modelo_valoracion.xlsx
+++ b/data/valuations/DE/DE_modelo_valoracion.xlsx
@@ -638,19 +638,19 @@
         </is>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.091</v>
+        <v>-0.0342</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.07100000000000001</v>
+        <v>-0.0308</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.051</v>
+        <v>-0.0274</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-0.031</v>
+        <v>-0.0239</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>-0.011</v>
+        <v>-0.0205</v>
       </c>
     </row>
     <row r="9">
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.07435</v>
+        <v>-0.0342</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.05435</v>
+        <v>-0.0308</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.03435000000000001</v>
+        <v>-0.0274</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>-0.01435</v>
+        <v>-0.0239</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.005650000000000002</v>
+        <v>-0.0205</v>
       </c>
     </row>
     <row r="10">
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.10765</v>
+        <v>-0.0342</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.08764999999999998</v>
+        <v>-0.0308</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.06764999999999999</v>
+        <v>-0.0274</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-0.04764999999999998</v>
+        <v>-0.0239</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>-0.02764999999999998</v>
+        <v>-0.0205</v>
       </c>
     </row>
     <row r="11">
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.3669251909068355</v>
+        <v>0.3569251909068355</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.3669251909068355</v>
+        <v>0.3569251909068355</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.3669251909068355</v>
+        <v>0.3569251909068355</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.3669251909068355</v>
+        <v>0.3569251909068355</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.3669251909068355</v>
+        <v>0.3569251909068355</v>
       </c>
     </row>
     <row r="17">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.3469251909068355</v>
+        <v>0.3569251909068355</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.3469251909068355</v>
+        <v>0.3569251909068355</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.3469251909068355</v>
+        <v>0.3569251909068355</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.3469251909068355</v>
+        <v>0.3569251909068355</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.3469251909068355</v>
+        <v>0.3569251909068355</v>
       </c>
     </row>
     <row r="18">
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.07669141166514645</v>
+        <v>0.08169141166514646</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.07669141166514645</v>
+        <v>0.08169141166514646</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.07669141166514645</v>
+        <v>0.08169141166514646</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.07669141166514645</v>
+        <v>0.08169141166514646</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.07669141166514645</v>
+        <v>0.08169141166514646</v>
       </c>
     </row>
     <row r="22">
@@ -912,19 +912,19 @@
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.08669141166514646</v>
+        <v>0.08169141166514646</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.08669141166514646</v>
+        <v>0.08169141166514646</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.08669141166514646</v>
+        <v>0.08169141166514646</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.08669141166514646</v>
+        <v>0.08169141166514646</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.08669141166514646</v>
+        <v>0.08169141166514646</v>
       </c>
     </row>
     <row r="23">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.0872</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="36">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.0772</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="37">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="38">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41">
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="C41" s="9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43">
@@ -3727,202 +3727,202 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>7x</t>
+          <t>8x</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>9x</t>
+          <t>10x</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>11x</t>
+          <t>12x</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>13x</t>
+          <t>14x</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>15x</t>
+          <t>16x</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.0572</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*7/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*8/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*9/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*10/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*11/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*12/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*13/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*14/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*15/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*16/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.0672</v>
+        <v>0.08</v>
       </c>
       <c r="C40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*7/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*8/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*9/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*10/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*11/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*12/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*13/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*14/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*15/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*16/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.0772</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="C41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*7/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*8/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*9/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*10/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*11/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*12/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*13/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*14/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*15/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*16/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.0872</v>
+        <v>0.1</v>
       </c>
       <c r="C42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*7/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*8/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*9/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*10/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*11/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*12/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*13/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*14/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*15/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*16/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="C43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*7/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*8/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*9/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*10/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*11/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*12/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*13/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*14/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*15/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*16/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.1072</v>
+        <v>0.12</v>
       </c>
       <c r="C44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*7/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*8/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*9/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*10/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*11/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*12/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*13/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*14/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*15/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*16/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.1172</v>
+        <v>0.13</v>
       </c>
       <c r="C45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*7/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*8/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*9/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*10/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*11/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*12/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*13/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*14/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*15/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*16/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>

--- a/data/valuations/DE/DE_modelo_valoracion.xlsx
+++ b/data/valuations/DE/DE_modelo_valoracion.xlsx
@@ -638,19 +638,19 @@
         </is>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.0342</v>
+        <v>-0.03</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.0308</v>
+        <v>0.05</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.0274</v>
+        <v>0.08</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-0.0239</v>
+        <v>0.06</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>-0.0205</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="9">
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.0342</v>
+        <v>0</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.0308</v>
+        <v>0.08</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.0274</v>
+        <v>0.1</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>-0.0239</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>-0.0205</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="10">
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.0342</v>
+        <v>-0.05</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.0308</v>
+        <v>0.03</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.0274</v>
+        <v>0.05</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-0.0239</v>
+        <v>0.05</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>-0.0205</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="11">
@@ -775,19 +775,19 @@
         </is>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.3569251909068355</v>
+        <v>0.357</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.3569251909068355</v>
+        <v>0.357</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.3569251909068355</v>
+        <v>0.357</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.3569251909068355</v>
+        <v>0.357</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.3569251909068355</v>
+        <v>0.357</v>
       </c>
     </row>
     <row r="16">
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.3569251909068355</v>
+        <v>0.37</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.3569251909068355</v>
+        <v>0.37</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.3569251909068355</v>
+        <v>0.37</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.3569251909068355</v>
+        <v>0.37</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.3569251909068355</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="17">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.3569251909068355</v>
+        <v>0.345</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.3569251909068355</v>
+        <v>0.345</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.3569251909068355</v>
+        <v>0.345</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.3569251909068355</v>
+        <v>0.345</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.3569251909068355</v>
+        <v>0.345</v>
       </c>
     </row>
     <row r="18">
@@ -868,19 +868,19 @@
         </is>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.08169141166514646</v>
+        <v>0.082</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.08169141166514646</v>
+        <v>0.082</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.08169141166514646</v>
+        <v>0.082</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.08169141166514646</v>
+        <v>0.082</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.08169141166514646</v>
+        <v>0.082</v>
       </c>
     </row>
     <row r="21">
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.08169141166514646</v>
+        <v>0.078</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.08169141166514646</v>
+        <v>0.078</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.08169141166514646</v>
+        <v>0.078</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.08169141166514646</v>
+        <v>0.078</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.08169141166514646</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="22">
@@ -912,19 +912,19 @@
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.08169141166514646</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.08169141166514646</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.08169141166514646</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.08169141166514646</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.08169141166514646</v>
+        <v>0.08500000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.04262228268028432</v>
+        <v>0.043</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.04262228268028432</v>
+        <v>0.043</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.04262228268028432</v>
+        <v>0.043</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.04262228268028432</v>
+        <v>0.043</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.04262228268028432</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="26">
@@ -983,19 +983,19 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.04262228268028432</v>
+        <v>0.043</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.04262228268028432</v>
+        <v>0.043</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.04262228268028432</v>
+        <v>0.043</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.04262228268028432</v>
+        <v>0.043</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.04262228268028432</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="27">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.04262228268028432</v>
+        <v>0.043</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.04262228268028432</v>
+        <v>0.043</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.04262228268028432</v>
+        <v>0.043</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.04262228268028432</v>
+        <v>0.043</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.04262228268028432</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="28">
@@ -1054,19 +1054,19 @@
         </is>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.04051138733746389</v>
+        <v>0.04</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.04051138733746389</v>
+        <v>0.04</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.04051138733746389</v>
+        <v>0.04</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.04051138733746389</v>
+        <v>0.04</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.04051138733746389</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="31">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.08441019330630305</v>
+        <v>0.08</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.08441019330630305</v>
+        <v>0.08</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.08441019330630305</v>
+        <v>0.08</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.08441019330630305</v>
+        <v>0.08</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.08441019330630305</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="32">
@@ -1098,19 +1098,19 @@
         </is>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.187992241799769</v>
+        <v>0.19</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.187992241799769</v>
+        <v>0.19</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.187992241799769</v>
+        <v>0.19</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.187992241799769</v>
+        <v>0.19</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.187992241799769</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="34">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.1</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="36">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.1</v>
+        <v>0.08500000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.1</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="38">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41">
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="C41" s="9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43">
@@ -3727,202 +3727,202 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>8x</t>
+          <t>9x</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>10x</t>
+          <t>11x</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>12x</t>
+          <t>13x</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>14x</t>
+          <t>15x</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>16x</t>
+          <t>17x</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="C39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*8/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*9/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*10/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*11/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*12/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*13/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*14/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*15/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*16/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*17/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="C40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*8/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*9/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*10/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*11/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*12/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*13/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*14/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*15/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*16/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*17/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*8/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*9/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*10/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*11/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*12/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*13/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*14/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*15/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*16/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*17/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.1</v>
+        <v>0.095</v>
       </c>
       <c r="C42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*8/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*9/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*10/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*11/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*12/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*13/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*14/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*15/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*16/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*17/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.11</v>
+        <v>0.105</v>
       </c>
       <c r="C43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*8/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*9/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*10/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*11/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*12/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*13/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*14/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*15/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*16/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*17/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.12</v>
+        <v>0.115</v>
       </c>
       <c r="C44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*8/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*9/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*10/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*11/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*12/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*13/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*14/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*15/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*16/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*17/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.13</v>
+        <v>0.125</v>
       </c>
       <c r="C45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*8/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*9/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*10/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*11/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*12/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*13/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*14/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*15/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*16/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*17/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>

--- a/data/valuations/DE/DE_modelo_valoracion.xlsx
+++ b/data/valuations/DE/DE_modelo_valoracion.xlsx
@@ -638,19 +638,19 @@
         </is>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.03</v>
+        <v>-0.0342</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.05</v>
+        <v>-0.0308</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.08</v>
+        <v>-0.0274</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.06</v>
+        <v>-0.0239</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.04</v>
+        <v>-0.0205</v>
       </c>
     </row>
     <row r="9">
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0</v>
+        <v>-0.0342</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.08</v>
+        <v>-0.0308</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.1</v>
+        <v>-0.0274</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.0239</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.05</v>
+        <v>-0.0205</v>
       </c>
     </row>
     <row r="10">
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.05</v>
+        <v>-0.0342</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03</v>
+        <v>-0.0308</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.05</v>
+        <v>-0.0274</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.05</v>
+        <v>-0.0239</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.03</v>
+        <v>-0.0205</v>
       </c>
     </row>
     <row r="11">
@@ -775,19 +775,19 @@
         </is>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.357</v>
+        <v>0.3569251909068355</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.357</v>
+        <v>0.3569251909068355</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.357</v>
+        <v>0.3569251909068355</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.357</v>
+        <v>0.3569251909068355</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.357</v>
+        <v>0.3569251909068355</v>
       </c>
     </row>
     <row r="16">
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.37</v>
+        <v>0.3569251909068355</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.37</v>
+        <v>0.3569251909068355</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.37</v>
+        <v>0.3569251909068355</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.37</v>
+        <v>0.3569251909068355</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.37</v>
+        <v>0.3569251909068355</v>
       </c>
     </row>
     <row r="17">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.345</v>
+        <v>0.3569251909068355</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.345</v>
+        <v>0.3569251909068355</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.345</v>
+        <v>0.3569251909068355</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.345</v>
+        <v>0.3569251909068355</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.345</v>
+        <v>0.3569251909068355</v>
       </c>
     </row>
     <row r="18">
@@ -868,19 +868,19 @@
         </is>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.082</v>
+        <v>0.08169141166514646</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.082</v>
+        <v>0.08169141166514646</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.082</v>
+        <v>0.08169141166514646</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.082</v>
+        <v>0.08169141166514646</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.082</v>
+        <v>0.08169141166514646</v>
       </c>
     </row>
     <row r="21">
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.078</v>
+        <v>0.08169141166514646</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.078</v>
+        <v>0.08169141166514646</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.078</v>
+        <v>0.08169141166514646</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.078</v>
+        <v>0.08169141166514646</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.078</v>
+        <v>0.08169141166514646</v>
       </c>
     </row>
     <row r="22">
@@ -912,19 +912,19 @@
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08169141166514646</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08169141166514646</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08169141166514646</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08169141166514646</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08169141166514646</v>
       </c>
     </row>
     <row r="23">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.043</v>
+        <v>0.04262228268028432</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.043</v>
+        <v>0.04262228268028432</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.043</v>
+        <v>0.04262228268028432</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.043</v>
+        <v>0.04262228268028432</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.043</v>
+        <v>0.04262228268028432</v>
       </c>
     </row>
     <row r="26">
@@ -983,19 +983,19 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.043</v>
+        <v>0.04262228268028432</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.043</v>
+        <v>0.04262228268028432</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.043</v>
+        <v>0.04262228268028432</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.043</v>
+        <v>0.04262228268028432</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.043</v>
+        <v>0.04262228268028432</v>
       </c>
     </row>
     <row r="27">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.043</v>
+        <v>0.04262228268028432</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.043</v>
+        <v>0.04262228268028432</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.043</v>
+        <v>0.04262228268028432</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.043</v>
+        <v>0.04262228268028432</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.043</v>
+        <v>0.04262228268028432</v>
       </c>
     </row>
     <row r="28">
@@ -1054,19 +1054,19 @@
         </is>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04051138733746389</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04051138733746389</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04051138733746389</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04051138733746389</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04051138733746389</v>
       </c>
     </row>
     <row r="31">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.08</v>
+        <v>0.08441019330630305</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.08</v>
+        <v>0.08441019330630305</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.08</v>
+        <v>0.08441019330630305</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.08</v>
+        <v>0.08441019330630305</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.08</v>
+        <v>0.08441019330630305</v>
       </c>
     </row>
     <row r="32">
@@ -1098,19 +1098,19 @@
         </is>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.19</v>
+        <v>0.187992241799769</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.19</v>
+        <v>0.187992241799769</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.19</v>
+        <v>0.187992241799769</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.19</v>
+        <v>0.187992241799769</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.19</v>
+        <v>0.187992241799769</v>
       </c>
     </row>
     <row r="34">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.095</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="36">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="37">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.105</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="38">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41">
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="C41" s="9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43">
@@ -2420,23 +2420,23 @@
         <v>4241</v>
       </c>
       <c r="G20" s="8">
-        <f>-G15*Assumptions!G24</f>
+        <f>-G15*Assumptions!G23</f>
         <v/>
       </c>
       <c r="H20" s="8">
-        <f>-H15*Assumptions!H24</f>
+        <f>-H15*Assumptions!H23</f>
         <v/>
       </c>
       <c r="I20" s="8">
-        <f>-I15*Assumptions!I24</f>
+        <f>-I15*Assumptions!I23</f>
         <v/>
       </c>
       <c r="J20" s="8">
-        <f>-J15*Assumptions!J24</f>
+        <f>-J15*Assumptions!J23</f>
         <v/>
       </c>
       <c r="K20" s="8">
-        <f>-K15*Assumptions!K24</f>
+        <f>-K15*Assumptions!K23</f>
         <v/>
       </c>
     </row>
@@ -2459,23 +2459,23 @@
         <v>2311</v>
       </c>
       <c r="G21" s="8">
-        <f>-G15*Assumptions!G30</f>
+        <f>-G15*Assumptions!G28</f>
         <v/>
       </c>
       <c r="H21" s="8">
-        <f>-H15*Assumptions!H30</f>
+        <f>-H15*Assumptions!H28</f>
         <v/>
       </c>
       <c r="I21" s="8">
-        <f>-I15*Assumptions!I30</f>
+        <f>-I15*Assumptions!I28</f>
         <v/>
       </c>
       <c r="J21" s="8">
-        <f>-J15*Assumptions!J30</f>
+        <f>-J15*Assumptions!J28</f>
         <v/>
       </c>
       <c r="K21" s="8">
-        <f>-K15*Assumptions!K30</f>
+        <f>-K15*Assumptions!K28</f>
         <v/>
       </c>
     </row>
@@ -2498,23 +2498,23 @@
         <v>2229</v>
       </c>
       <c r="G22" s="8">
-        <f>-G15*Assumptions!G32</f>
+        <f>-G15*Assumptions!G30</f>
         <v/>
       </c>
       <c r="H22" s="8">
-        <f>-H15*Assumptions!H32</f>
+        <f>-H15*Assumptions!H30</f>
         <v/>
       </c>
       <c r="I22" s="8">
-        <f>-I15*Assumptions!I32</f>
+        <f>-I15*Assumptions!I30</f>
         <v/>
       </c>
       <c r="J22" s="8">
-        <f>-J15*Assumptions!J32</f>
+        <f>-J15*Assumptions!J30</f>
         <v/>
       </c>
       <c r="K22" s="8">
-        <f>-K15*Assumptions!K32</f>
+        <f>-K15*Assumptions!K30</f>
         <v/>
       </c>
     </row>
@@ -2786,23 +2786,23 @@
         <v>1259</v>
       </c>
       <c r="G31" s="8">
-        <f>-ABS(G30)*Assumptions!G34</f>
+        <f>-ABS(G30)*Assumptions!G32</f>
         <v/>
       </c>
       <c r="H31" s="8">
-        <f>-ABS(H30)*Assumptions!H34</f>
+        <f>-ABS(H30)*Assumptions!H32</f>
         <v/>
       </c>
       <c r="I31" s="8">
-        <f>-ABS(I30)*Assumptions!I34</f>
+        <f>-ABS(I30)*Assumptions!I32</f>
         <v/>
       </c>
       <c r="J31" s="8">
-        <f>-ABS(J30)*Assumptions!J34</f>
+        <f>-ABS(J30)*Assumptions!J32</f>
         <v/>
       </c>
       <c r="K31" s="8">
-        <f>-ABS(K30)*Assumptions!K34</f>
+        <f>-ABS(K30)*Assumptions!K32</f>
         <v/>
       </c>
     </row>
@@ -3091,23 +3091,23 @@
         <v>-4228</v>
       </c>
       <c r="G42" s="8">
-        <f>-ABS(G15)*Assumptions!G33</f>
+        <f>-ABS(G15)*Assumptions!G31</f>
         <v/>
       </c>
       <c r="H42" s="8">
-        <f>-ABS(H15)*Assumptions!H33</f>
+        <f>-ABS(H15)*Assumptions!H31</f>
         <v/>
       </c>
       <c r="I42" s="8">
-        <f>-ABS(I15)*Assumptions!I33</f>
+        <f>-ABS(I15)*Assumptions!I31</f>
         <v/>
       </c>
       <c r="J42" s="8">
-        <f>-ABS(J15)*Assumptions!J33</f>
+        <f>-ABS(J15)*Assumptions!J31</f>
         <v/>
       </c>
       <c r="K42" s="8">
-        <f>-ABS(K15)*Assumptions!K33</f>
+        <f>-ABS(K15)*Assumptions!K31</f>
         <v/>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>575.71</v>
+        <v>542.1799999999999</v>
       </c>
     </row>
     <row r="4">
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="C15" s="7">
-        <f>Assumptions!C42</f>
+        <f>Assumptions!C38</f>
         <v/>
       </c>
     </row>
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="C16" s="10">
-        <f>Assumptions!C48</f>
+        <f>Assumptions!C43</f>
         <v/>
       </c>
     </row>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="C32" s="18" t="n">
-        <v>270.107282</v>
+        <v>269.937425</v>
       </c>
     </row>
     <row r="33">
@@ -3687,7 +3687,7 @@
         </is>
       </c>
       <c r="C33" s="19">
-        <f>C30/C32</f>
+        <f>(C30/C32)*1</f>
         <v/>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/575.71-1</f>
+        <f>C33/542.18-1</f>
         <v/>
       </c>
     </row>
@@ -3727,202 +3727,202 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>9x</t>
+          <t>8x</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>11x</t>
+          <t>10x</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>13x</t>
+          <t>12x</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>15x</t>
+          <t>14x</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>17x</t>
+          <t>16x</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.065</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*9/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*8/(1+$A$39)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
       <c r="D39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*11/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*10/(1+$A$39)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
       <c r="E39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*13/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*12/(1+$A$39)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
       <c r="F39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*15/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*14/(1+$A$39)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
       <c r="G39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*17/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*16/(1+$A$39)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.075</v>
+        <v>0.08</v>
       </c>
       <c r="C40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*9/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*8/(1+$A$40)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
       <c r="D40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*11/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*10/(1+$A$40)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
       <c r="E40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*13/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*12/(1+$A$40)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
       <c r="F40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*15/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*14/(1+$A$40)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
       <c r="G40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*17/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*16/(1+$A$40)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="C41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*9/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*8/(1+$A$41)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
       <c r="D41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*11/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*10/(1+$A$41)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
       <c r="E41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*13/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*12/(1+$A$41)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
       <c r="F41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*15/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*14/(1+$A$41)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
       <c r="G41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*17/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*16/(1+$A$41)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.095</v>
+        <v>0.1</v>
       </c>
       <c r="C42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*9/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*8/(1+$A$42)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
       <c r="D42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*11/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*10/(1+$A$42)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*13/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*12/(1+$A$42)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
       <c r="F42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*15/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*14/(1+$A$42)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
       <c r="G42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*17/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*16/(1+$A$42)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.105</v>
+        <v>0.11</v>
       </c>
       <c r="C43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*9/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*8/(1+$A$43)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
       <c r="D43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*11/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*10/(1+$A$43)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
       <c r="E43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*13/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*12/(1+$A$43)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
       <c r="F43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*15/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*14/(1+$A$43)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
       <c r="G43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*17/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*16/(1+$A$43)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.115</v>
+        <v>0.12</v>
       </c>
       <c r="C44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*9/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*8/(1+$A$44)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
       <c r="D44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*11/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*10/(1+$A$44)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
       <c r="E44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*13/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*12/(1+$A$44)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
       <c r="F44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*15/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*14/(1+$A$44)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
       <c r="G44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*17/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*16/(1+$A$44)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.125</v>
+        <v>0.13</v>
       </c>
       <c r="C45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*9/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*8/(1+$A$45)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
       <c r="D45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*11/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*10/(1+$A$45)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
       <c r="E45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*13/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*12/(1+$A$45)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
       <c r="F45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*15/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*14/(1+$A$45)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
       <c r="G45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*17/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>((G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*16/(1+$A$45)^5+$C$29)/$C$32)*1</f>
         <v/>
       </c>
     </row>
